--- a/Data/GP2_Feedintake.xlsx
+++ b/Data/GP2_Feedintake.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Guinea-Pig-data_2\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68A0AEA7-0302-44A7-9D05-DB8C147E6B4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{628FBB48-FE96-469C-A029-B554C1FBBC04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-165" yWindow="-165" windowWidth="29130" windowHeight="15810" xr2:uid="{0A0BFAF5-E300-4036-8761-75E43C7CE86B}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{0A0BFAF5-E300-4036-8761-75E43C7CE86B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -464,7 +464,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79B447F4-728A-4B0B-8AEC-CE918F05B364}">
-  <dimension ref="A1:I1025"/>
+  <dimension ref="A1:J1025"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="12.90625" bestFit="1" customWidth="1"/>
@@ -8155,7 +8155,7 @@
         <v>28.4</v>
       </c>
     </row>
-    <row r="257" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="257" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A257" s="1" t="s">
         <v>0</v>
       </c>
@@ -8184,8 +8184,12 @@
         <f t="shared" si="3"/>
         <v>26</v>
       </c>
-    </row>
-    <row r="258" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J257">
+        <f>AVERAGE(I2:I257)</f>
+        <v>27.303580729166658</v>
+      </c>
+    </row>
+    <row r="258" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A258" s="1" t="s">
         <v>3</v>
       </c>
@@ -8215,7 +8219,7 @@
         <v>19.399999999999999</v>
       </c>
     </row>
-    <row r="259" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="259" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A259" s="1" t="s">
         <v>3</v>
       </c>
@@ -8245,7 +8249,7 @@
         <v>19.2</v>
       </c>
     </row>
-    <row r="260" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="260" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A260" s="1" t="s">
         <v>3</v>
       </c>
@@ -8275,7 +8279,7 @@
         <v>19.600000000000001</v>
       </c>
     </row>
-    <row r="261" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="261" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A261" s="1" t="s">
         <v>3</v>
       </c>
@@ -8305,7 +8309,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="262" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="262" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A262" s="1" t="s">
         <v>3</v>
       </c>
@@ -8335,7 +8339,7 @@
         <v>27.2</v>
       </c>
     </row>
-    <row r="263" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="263" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A263" s="1" t="s">
         <v>3</v>
       </c>
@@ -8365,7 +8369,7 @@
         <v>27.6</v>
       </c>
     </row>
-    <row r="264" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="264" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A264" s="1" t="s">
         <v>3</v>
       </c>
@@ -8395,7 +8399,7 @@
         <v>26.6</v>
       </c>
     </row>
-    <row r="265" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="265" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A265" s="1" t="s">
         <v>3</v>
       </c>
@@ -8425,7 +8429,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="266" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="266" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A266" s="1" t="s">
         <v>3</v>
       </c>
@@ -8455,7 +8459,7 @@
         <v>25.8</v>
       </c>
     </row>
-    <row r="267" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="267" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A267" s="1" t="s">
         <v>3</v>
       </c>
@@ -8485,7 +8489,7 @@
         <v>24.8</v>
       </c>
     </row>
-    <row r="268" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="268" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A268" s="1" t="s">
         <v>3</v>
       </c>
@@ -8515,7 +8519,7 @@
         <v>22.2</v>
       </c>
     </row>
-    <row r="269" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="269" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A269" s="1" t="s">
         <v>3</v>
       </c>
@@ -8545,7 +8549,7 @@
         <v>27.6</v>
       </c>
     </row>
-    <row r="270" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="270" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A270" s="1" t="s">
         <v>3</v>
       </c>
@@ -8575,7 +8579,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="271" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="271" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A271" s="1" t="s">
         <v>3</v>
       </c>
@@ -8605,7 +8609,7 @@
         <v>28.4</v>
       </c>
     </row>
-    <row r="272" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="272" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A272" s="1" t="s">
         <v>3</v>
       </c>
@@ -15835,7 +15839,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="513" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="513" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A513" s="1" t="s">
         <v>3</v>
       </c>
@@ -15864,8 +15868,12 @@
         <f t="shared" si="7"/>
         <v>30</v>
       </c>
-    </row>
-    <row r="514" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J513">
+        <f>AVERAGE(I258:I513)</f>
+        <v>27.156835937500006</v>
+      </c>
+    </row>
+    <row r="514" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A514" s="1" t="s">
         <v>4</v>
       </c>
@@ -15895,7 +15903,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="515" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="515" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A515" s="1" t="s">
         <v>4</v>
       </c>
@@ -15925,7 +15933,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="516" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="516" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A516" s="1" t="s">
         <v>4</v>
       </c>
@@ -15955,7 +15963,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="517" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="517" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A517" s="1" t="s">
         <v>4</v>
       </c>
@@ -15985,7 +15993,7 @@
         <v>16.600000000000001</v>
       </c>
     </row>
-    <row r="518" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="518" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A518" s="1" t="s">
         <v>4</v>
       </c>
@@ -16015,7 +16023,7 @@
         <v>28.4</v>
       </c>
     </row>
-    <row r="519" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="519" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A519" s="1" t="s">
         <v>4</v>
       </c>
@@ -16045,7 +16053,7 @@
         <v>29.2</v>
       </c>
     </row>
-    <row r="520" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="520" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A520" s="1" t="s">
         <v>4</v>
       </c>
@@ -16075,7 +16083,7 @@
         <v>26.6</v>
       </c>
     </row>
-    <row r="521" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="521" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A521" s="1" t="s">
         <v>4</v>
       </c>
@@ -16105,7 +16113,7 @@
         <v>22.6</v>
       </c>
     </row>
-    <row r="522" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="522" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A522" s="1" t="s">
         <v>4</v>
       </c>
@@ -16135,7 +16143,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="523" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="523" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A523" s="1" t="s">
         <v>4</v>
       </c>
@@ -16165,7 +16173,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="524" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="524" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A524" s="1" t="s">
         <v>4</v>
       </c>
@@ -16195,7 +16203,7 @@
         <v>24.6</v>
       </c>
     </row>
-    <row r="525" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="525" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A525" s="1" t="s">
         <v>4</v>
       </c>
@@ -16225,7 +16233,7 @@
         <v>21.6</v>
       </c>
     </row>
-    <row r="526" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="526" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A526" s="1" t="s">
         <v>4</v>
       </c>
@@ -16255,7 +16263,7 @@
         <v>29.4</v>
       </c>
     </row>
-    <row r="527" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="527" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A527" s="1" t="s">
         <v>4</v>
       </c>
@@ -16285,7 +16293,7 @@
         <v>29.4</v>
       </c>
     </row>
-    <row r="528" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="528" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A528" s="1" t="s">
         <v>4</v>
       </c>
@@ -23515,7 +23523,7 @@
         <v>31.75</v>
       </c>
     </row>
-    <row r="769" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="769" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A769" s="1" t="s">
         <v>4</v>
       </c>
@@ -23544,8 +23552,12 @@
         <f t="shared" si="11"/>
         <v>27.2</v>
       </c>
-    </row>
-    <row r="770" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J769">
+        <f>AVERAGE(I514:I769)</f>
+        <v>26.329687500000002</v>
+      </c>
+    </row>
+    <row r="770" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A770" s="1" t="s">
         <v>5</v>
       </c>
@@ -23575,7 +23587,7 @@
         <v>18.399999999999999</v>
       </c>
     </row>
-    <row r="771" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="771" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A771" s="1" t="s">
         <v>5</v>
       </c>
@@ -23605,7 +23617,7 @@
         <v>19.8</v>
       </c>
     </row>
-    <row r="772" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="772" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A772" s="1" t="s">
         <v>5</v>
       </c>
@@ -23635,7 +23647,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="773" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="773" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A773" s="1" t="s">
         <v>5</v>
       </c>
@@ -23665,7 +23677,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="774" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="774" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A774" s="1" t="s">
         <v>5</v>
       </c>
@@ -23695,7 +23707,7 @@
         <v>21.8</v>
       </c>
     </row>
-    <row r="775" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="775" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A775" s="1" t="s">
         <v>5</v>
       </c>
@@ -23725,7 +23737,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="776" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="776" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A776" s="1" t="s">
         <v>5</v>
       </c>
@@ -23755,7 +23767,7 @@
         <v>25.8</v>
       </c>
     </row>
-    <row r="777" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="777" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A777" s="1" t="s">
         <v>5</v>
       </c>
@@ -23785,7 +23797,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="778" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="778" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A778" s="1" t="s">
         <v>5</v>
       </c>
@@ -23815,7 +23827,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="779" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="779" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A779" s="1" t="s">
         <v>5</v>
       </c>
@@ -23845,7 +23857,7 @@
         <v>20.399999999999999</v>
       </c>
     </row>
-    <row r="780" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="780" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A780" s="1" t="s">
         <v>5</v>
       </c>
@@ -23875,7 +23887,7 @@
         <v>24.8</v>
       </c>
     </row>
-    <row r="781" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="781" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A781" s="1" t="s">
         <v>5</v>
       </c>
@@ -23905,7 +23917,7 @@
         <v>28.4</v>
       </c>
     </row>
-    <row r="782" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="782" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A782" s="1" t="s">
         <v>5</v>
       </c>
@@ -23935,7 +23947,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="783" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="783" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A783" s="1" t="s">
         <v>5</v>
       </c>
@@ -23965,7 +23977,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="784" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="784" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A784" s="1" t="s">
         <v>5</v>
       </c>
@@ -31195,7 +31207,7 @@
         <v>28.8</v>
       </c>
     </row>
-    <row r="1025" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1025" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A1025" s="1" t="s">
         <v>5</v>
       </c>
@@ -31223,6 +31235,10 @@
       <c r="I1025" s="1">
         <f t="shared" si="15"/>
         <v>28</v>
+      </c>
+      <c r="J1025">
+        <f>AVERAGE(I770:I1025)</f>
+        <v>26.676367187499999</v>
       </c>
     </row>
   </sheetData>
